--- a/reports/一级子公司A_利润表_2026-04.xlsx
+++ b/reports/一级子公司A_利润表_2026-04.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>175924088</v>
+        <v>180387762</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>171398892</v>
+        <v>171967795</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>620926969</v>
+        <v>620678945</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>699233</v>
+        <v>702341</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2632546</v>
+        <v>2641805</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>606789</v>
+        <v>608130</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2284172</v>
+        <v>2292067</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>516089</v>
+        <v>514244</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1937303</v>
+        <v>1941329</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>474154</v>
+        <v>472192</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1781800</v>
+        <v>1784248</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>256889</v>
+        <v>256268</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>967689</v>
+        <v>968421</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>206007</v>
+        <v>204909</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>774558</v>
+        <v>773705</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>173164927</v>
+        <v>177629678</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>168639731</v>
+        <v>169209711</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>87010860</v>
+        <v>86718339</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>302511167</v>
+        <v>301569915</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1597874</v>
+        <v>1595761</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>6003966</v>
+        <v>5983687</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1444427</v>
+        <v>1445991</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>5423995</v>
+        <v>5411475</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>76869497</v>
+        <v>77704605</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>290144643</v>
+        <v>290785616</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1645275</v>
+        <v>1656865</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>6194093</v>
+        <v>6207064</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>723419</v>
+        <v>724501</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>2712979</v>
+        <v>2717038</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2575478</v>
+        <v>2581903</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>9682585</v>
+        <v>9714198</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1129936</v>
+        <v>1135591</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>4257507</v>
+        <v>4273639</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4432275</v>
+        <v>4430523</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>16655625</v>
+        <v>16703838</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>92921</v>
+        <v>92516</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>358649</v>
+        <v>371713</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2339187</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>8839853</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1557741</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>5885444</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>117417202</v>
+        <v>125811376</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>104875781</v>
+        <v>104852183</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>102713285</v>
+        <v>102691871</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>387040908</v>
+        <v>386077979</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2162496</v>
+        <v>2160312</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>8132375</v>
+        <v>8107110</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>3918786</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>14678086</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1256509</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>4701586</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>786436</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2942217</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>944296</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>3535365</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>708002</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2654609</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>471445</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1771136</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>392149</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1476358</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1807500</v>
+        <v>1801891</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>6781565</v>
+        <v>6796980</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1391071</v>
+        <v>1387103</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>5228818</v>
+        <v>5239220</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1129911</v>
+        <v>1128414</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>4257491</v>
+        <v>4264392</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8553548</v>
+        <v>8505560</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>32147705</v>
+        <v>32133639</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>361366</v>
+        <v>358610</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1393360</v>
+        <v>1353424</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>689096</v>
+        <v>687095</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2673247</v>
+        <v>2753530</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>781100</v>
+        <v>687095</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3030637</v>
+        <v>2753530</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>92889</v>
+        <v>92621</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>358582</v>
+        <v>369630</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>352792</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1405318</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>687310</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2571582</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>235962</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>938961</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>177057</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>705156</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>294968</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1176638</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>981967</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>3690120</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>156816</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>628232</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>117354</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>471052</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>195179</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>784480</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>136402</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>548504</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>97344</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>391268</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>77878</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>312618</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>58464</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>234232</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>55747725</v>
+        <v>54231397</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>64628296</v>
+        <v>60642558</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>392101</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1468134</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>98209</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>390803</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>154800</v>
+        <v>155254</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>598442</v>
+        <v>617832</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>55592925</v>
+        <v>54468244</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5445206</v>
+        <v>5484713</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>21132814</v>
+        <v>21884103</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>50147719</v>
+        <v>48983531</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>50147719</v>
+        <v>48983531</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>50147719</v>
+        <v>48983531</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>50147719</v>
+        <v>48983531</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>50147719</v>
+        <v>48983531</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
